--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-core-information-recipient.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-core-information-recipient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:49:50+00:00</t>
+    <t>2025-09-03T12:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1896,7 +1896,7 @@
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>

--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-core-information-recipient.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-core-information-recipient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
